--- a/江西通信/部门人名.xlsx
+++ b/江西通信/部门人名.xlsx
@@ -90,7 +90,7 @@
     <t>陈萍</t>
   </si>
   <si>
-    <t>质量部门</t>
+    <t>质量管理部门</t>
   </si>
   <si>
     <t>质量管理部</t>
@@ -558,7 +558,7 @@
       </bottom>
     </border>
   </borders>
-  <cellStyleXfs count="73">
+  <cellStyleXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
       <protection/>
@@ -587,6 +587,11 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
       <alignment/>
     </xf>
@@ -737,7 +742,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="59">
+  <cellStyles count="64">
     <cellStyle name="Normal" xfId="0"/>
     <cellStyle name="Percent" xfId="15"/>
     <cellStyle name="Currency" xfId="16"/>
@@ -749,54 +754,59 @@
     <cellStyle name="Currency [0]" xfId="22"/>
     <cellStyle name="Comma" xfId="23"/>
     <cellStyle name="Comma [0]" xfId="24"/>
-    <cellStyle name="千位分隔" xfId="25"/>
-    <cellStyle name="货币" xfId="26"/>
-    <cellStyle name="百分比" xfId="27"/>
-    <cellStyle name="千位分隔[0]" xfId="28"/>
-    <cellStyle name="货币[0]" xfId="29"/>
-    <cellStyle name="超链接" xfId="30"/>
-    <cellStyle name="已访问的超链接" xfId="31"/>
-    <cellStyle name="注释" xfId="32"/>
-    <cellStyle name="警告文本" xfId="33"/>
-    <cellStyle name="标题" xfId="34"/>
-    <cellStyle name="解释性文本" xfId="35"/>
-    <cellStyle name="标题 1" xfId="36"/>
-    <cellStyle name="标题 2" xfId="37"/>
-    <cellStyle name="标题 3" xfId="38"/>
-    <cellStyle name="标题 4" xfId="39"/>
-    <cellStyle name="输入" xfId="40"/>
-    <cellStyle name="输出" xfId="41"/>
-    <cellStyle name="计算" xfId="42"/>
-    <cellStyle name="检查单元格" xfId="43"/>
-    <cellStyle name="链接单元格" xfId="44"/>
-    <cellStyle name="汇总" xfId="45"/>
-    <cellStyle name="好" xfId="46"/>
-    <cellStyle name="差" xfId="47"/>
-    <cellStyle name="适中" xfId="48"/>
-    <cellStyle name="强调文字颜色 1" xfId="49"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="50"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="51"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="52"/>
-    <cellStyle name="强调文字颜色 2" xfId="53"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="54"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="55"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="56"/>
-    <cellStyle name="强调文字颜色 3" xfId="57"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="58"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="59"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="60"/>
-    <cellStyle name="强调文字颜色 4" xfId="61"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="62"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="63"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="64"/>
-    <cellStyle name="强调文字颜色 5" xfId="65"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="66"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="67"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="68"/>
-    <cellStyle name="强调文字颜色 6" xfId="69"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="70"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="71"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="72"/>
+    <cellStyle name="Percent" xfId="25"/>
+    <cellStyle name="Currency" xfId="26"/>
+    <cellStyle name="Currency [0]" xfId="27"/>
+    <cellStyle name="Comma" xfId="28"/>
+    <cellStyle name="Comma [0]" xfId="29"/>
+    <cellStyle name="千位分隔" xfId="30"/>
+    <cellStyle name="货币" xfId="31"/>
+    <cellStyle name="百分比" xfId="32"/>
+    <cellStyle name="千位分隔[0]" xfId="33"/>
+    <cellStyle name="货币[0]" xfId="34"/>
+    <cellStyle name="超链接" xfId="35"/>
+    <cellStyle name="已访问的超链接" xfId="36"/>
+    <cellStyle name="注释" xfId="37"/>
+    <cellStyle name="警告文本" xfId="38"/>
+    <cellStyle name="标题" xfId="39"/>
+    <cellStyle name="解释性文本" xfId="40"/>
+    <cellStyle name="标题 1" xfId="41"/>
+    <cellStyle name="标题 2" xfId="42"/>
+    <cellStyle name="标题 3" xfId="43"/>
+    <cellStyle name="标题 4" xfId="44"/>
+    <cellStyle name="输入" xfId="45"/>
+    <cellStyle name="输出" xfId="46"/>
+    <cellStyle name="计算" xfId="47"/>
+    <cellStyle name="检查单元格" xfId="48"/>
+    <cellStyle name="链接单元格" xfId="49"/>
+    <cellStyle name="汇总" xfId="50"/>
+    <cellStyle name="好" xfId="51"/>
+    <cellStyle name="差" xfId="52"/>
+    <cellStyle name="适中" xfId="53"/>
+    <cellStyle name="强调文字颜色 1" xfId="54"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="55"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="56"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="57"/>
+    <cellStyle name="强调文字颜色 2" xfId="58"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="59"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="60"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="61"/>
+    <cellStyle name="强调文字颜色 3" xfId="62"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="63"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="64"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="65"/>
+    <cellStyle name="强调文字颜色 4" xfId="66"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="67"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="68"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="69"/>
+    <cellStyle name="强调文字颜色 5" xfId="70"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="71"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="72"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="73"/>
+    <cellStyle name="强调文字颜色 6" xfId="74"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="75"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="76"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="77"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
